--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_12_Full_159_Cau/Day_12_Ngan_Hang_Phan_04_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_12_Full_159_Cau/Day_12_Ngan_Hang_Phan_04_20_Cau.xlsx
@@ -641,7 +641,7 @@
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Xác định MCP server sống cùng process local hay qua remote endpoint trước khi chọn mô hình auth.</t>
+          <t>Giao thức Model Context Protocol (MCP) chạy qua stdio giữa các tiến trình cục bộ dựa trên ranh giới tin cậy (trust boundary) của tiến trình cha; tiến trình con thừa hưởng quyền và tin cậy trực tiếp từ tiến trình gọi.</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Xác định có user delegation hay không, rồi đối chiếu identity, phạm vi quyền và rotation.</t>
+          <t>Đối với dịch vụ nội bộ chạy tự động giữa các máy, mô hình xác thực tối ưu là sử dụng workload credential (như mTLS hoặc short-lived token) có phạm vi quyền hạn tối thiểu và cơ chế tự động xoay vòng định kỳ.</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hỏi điều gì xảy ra với cả header thiếu lẫn header sai trước khi handler được gọi.</t>
+          <t>Cơ chế xác thực API key an toàn trong FastAPI dependency: Từ chối ngay lập tức khi thiếu hoặc sai header, sử dụng thuật toán so sánh chuỗi thời gian không đổi (`secrets.compare_digest`) để chống timing attack, và truyền identity hợp lệ xuống handler.</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Identity hợp lệ có mặc nhiên được phép mọi thao tác không?</t>
+          <t>Xác thực (Authentication) chỉ chứng minh danh tính của bên gọi; hệ thống bắt buộc phải có bước phân quyền (Authorization) để bảo đảm bên gọi có quyền thao tác trên tài nguyên của tenant tương ứng.</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chọn các trường trả lời: ai bị giới hạn, thuật toán có tham số gì và retry lúc nào.</t>
+          <t>Chính sách rate limiting đúng chuẩn multi-tenant bao gồm: (b) khóa đếm phân cấp theo tenant+tier+route để chống noisy-neighbor, (c) cấu hình dung lượng burst và tốc độ nạp (token bucket), (e) phản hồi chuẩn HTTP 429 kèm header Retry-After.</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Áp đúng điều kiện xóa timestamp rồi đếm số mốc còn lại trước khi thêm mốc mới.</t>
+          <t>Thuật toán sliding window 60s: Tại thời điểm t=60, mốc t=0 thỏa mãn điều kiện t_event &lt;= now - 60 (0 &lt;= 0) nên bị loại khỏi cửa sổ trượt, số mốc còn lại là 2 (t=20, 40) &lt; giới hạn 3; do đó request tại t=60 được cho phép.</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>0.006</t>
+        </is>
+      </c>
       <c r="D16" s="3" t="n"/>
       <c r="E16" s="3" t="n"/>
       <c r="F16" s="3" t="n"/>
@@ -1175,7 +1179,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính token đầu vào và đầu ra riêng theo đơn vị 1M rồi cộng hai phần.</t>
+          <t>Chi phí ước tính: (1.000 input tokens * $2 / 1.000.000) + (500 output tokens * $8 / 1.000.000) = $0,002 + $0,004 = 0,006 USD.</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1261,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Cộng phần đã dùng với chi phí ước tính cho từng tenant, không gộp hai sổ.</t>
+          <t>Quản lý ngân sách multi-tenant: Tenant A đã dùng $9/$10, request mới ước tính $2 sẽ làm vượt trần ngân sách ($11 &gt; $10) nên phải bị từ chối; trong khi sổ chi tiêu của tenant B hoàn toàn độc lập và không bị ảnh hưởng.</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1343,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hỏi credential đã lộ còn được production chấp nhận hay phải vô hiệu ngay.</t>
+          <t>Khi secret bị commit nhầm lên git, dù đã xóa ở commit tiếp theo thì khóa cũ vẫn tồn tại trong lịch sử và có nguy cơ bị lộ; hành động đầu tiên bắt buộc phải là thu hồi và xoay vòng credential đó ngay lập tức.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_12_Full_159_Cau/Day_12_Ngan_Hang_Phan_04_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_12_Full_159_Cau/Day_12_Ngan_Hang_Phan_04_20_Cau.xlsx
@@ -672,10 +672,29 @@
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách ba lớp: remote transport, token audience/scope và vòng đời khác với stdio.
-Phân tích theo nguyên lý thiết kế: Tách ba lớp: remote transport, token audience/scope và vòng đời khác với stdio.</t>
+- [1.0 điểm] Thiết kế Remote HTTP Transport cho MCP thay thế stdio và kiến trúc hosting phân lập phiên độc lập.
+- [1.5 điểm] Xây dựng cơ chế Delegated Access với OAuth 2.0 / JWT mang đầy đủ các claims: sub, tenant_id, scopes.
+- [1.5 điểm] Thiết lập chặt chẽ Resource-Audience boundary kiểm tra claim `aud` chống Confused Deputy và cô lập dữ liệu chống tenant-hopping.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế Hosting Boundary (Remote HTTP Transport &amp; Tenant Isolation):
+   - Chuyển đổi Giao thức: Thay thế cơ chế stdio đơn tiến trình bằng Remote HTTP Transport (kết hợp Server-Sent Events cho truyền phát dữ liệu và HTTP POST cho gọi công cụ qua mã hóa TLS 1.3).
+   - Hosting Architecture: MCP Server được triển khai dưới dạng dịch vụ đám mây tập trung trong Private VPC, đứng sau Cloud API Gateway đóng vai trò Ingress Controller.
+   - Phân lập Phiên (Session Context Boundary): Mỗi kết nối client được gán một `SessionContext` độc lập trong bộ nhớ hoặc Redis; tuyệt đối không sử dụng biến tĩnh/toàn cục (global state) để tránh rò rỉ dữ liệu giữa các tenant.
+2. Thiết kế Xác thực và Truy cập Người dùng Ủy quyền (Authentication &amp; Delegated Access):
+   - Chuẩn Xác thực: Áp dụng OAuth 2.0 Token Exchange (RFC 8693) hoặc JSON Web Tokens (JWT) do Identity Provider (IdP) doanh nghiệp ký duyệt.
+   - Cấu trúc Claim Ủy quyền Bắt buộc trong Token:
+     + `sub`: Định danh người dùng cuối được ủy quyền (ví dụ `user_9876`).
+     + `tenant_id`: Định danh tổ chức sở hữu tài nguyên (ví dụ `tenant_alpha`).
+     + `scope`: Phạm vi công cụ MCP được phép gọi (ví dụ `mcp:tools:read mcp:tools:execute`).
+3. Thiết kế Ranh giới Khán giả Tài nguyên (Resource-Audience Boundary):
+   - Xác thực Claim Khán giả (`aud` - Audience):
+     + MCP Server bắt buộc phải kiểm tra claim `aud == https://mcp.enterprise.internal/tools`.
+     + Nếu client mang token có audience của một dịch vụ khác (ví dụ `https://api.model-provider.com`), MCP Server phải từ chối ngay lập tức với `HTTP 403 Forbidden` nhằm ngăn chặn tấn công giả mạo quyền ủy quyền (Confused Deputy Attack).
+   - Ngăn chặn Tenant-Hopping: Toàn bộ truy vấn dữ liệu từ các tool bên dưới bắt buộc phải tiêm điều kiện lọc `WHERE tenant_id = token.tenant_id` lấy từ token đã xác thực, cấm tin tưởng tenant_id gửi tự do từ request body.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Khi đưa Model Context Protocol (MCP) từ môi trường máy trạm đơn lẻ lên dịch vụ đám mây chia sẻ đa người thuê (Multi-Tenant Remote MCP), ranh giới bảo mật chuyển dịch từ mức tiến trình hệ điều hành sang mức giao thức mạng. Việc kết hợp xác thực đại diện người dùng (Delegated Access) và kiểm tra nghiêm ngặt Audience token bảo đảm tính toàn vẹn dữ liệu và ngăn chặn hoàn toàn việc truy cập trái phép giữa các tổ chức.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Model Context Protocol Specification - Remote Transports: https://modelcontextprotocol.io/ và RFC 8693 (OAuth 2.0 Token Exchange)</t>
         </is>
       </c>
     </row>
@@ -758,10 +777,32 @@
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Nối từng lỗi trong bối cảnh với gate xử lý nó và một dấu vết có thể quan sát.
-Phân tích theo nguyên lý thiết kế: Nối từng lỗi trong bối cảnh với gate xử lý nó và một dấu vết có thể quan sát.</t>
+- [1.0 điểm] Sắp xếp chính xác pipeline 4 cổng kiểm duyệt theo thứ tự chi phí tăng dần: Schema (400) -&gt; Auth (401) -&gt; Quota (429) -&gt; Budget (402/403).
+- [1.5 điểm] Thiết kế cơ chế ngắn mạch Middleware ngăn chặn tuyệt đối việc thực thi các bước sau khi cổng trước bị từ chối.
+- [1.5 điểm] Xây dựng bộ kiểm thử chứng minh với dấu vết metrics cụ thể khẳng định model_calls = 0 đối với từng loại lỗi từ chối.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Sắp xếp Luồng Kiểm duyệt Thất bại Sớm (Fail-Fast Gate Pipeline - Thứ tự Chi phí Tăng dần):
+   - Cổng 1 (Schema &amp; Body Validation Gate - Chi phí ~0.0001 ms CPU):
+     Kiểm tra cú pháp JSON, tính đầy đủ của các trường bắt buộc và định dạng payload. Nếu thân sai định dạng -&gt; Từ chối ngay với `HTTP 400 Bad Request`.
+   - Cổng 2 (Authentication &amp; Signature Verification Gate - Chi phí ~0.1 ms CPU):
+     Kiểm tra header Authorization, giải mã và xác thực chữ ký JWT. Nếu thiếu hoặc sai token -&gt; Từ chối ngay với `HTTP 401 Unauthorized`.
+   - Cổng 3 (Rate Limiting &amp; Tier Quota Gate - Chi phí ~1 ms Redis I/O):
+     Tra cứu số lượng yêu cầu trong cửa sổ thời gian của tenant trong Redis. Nếu đã hết hạn mức tốc độ -&gt; Từ chối ngay với `HTTP 429 Too Many Requests`.
+   - Cổng 4 (Budget &amp; Cost Pre-Check Gate - Chi phí ~2 ms Tokenizer calculation):
+     Đếm số lượng token đầu vào (prompt tokens) và ước tính trần chi phí tối đa của request. Nếu vượt quá ngân sách còn lại của tenant -&gt; Từ chối ngay với `HTTP 402 Payment Required` hoặc `403 Forbidden`.
+   - Cổng Cuối (Model Execution &amp; Paid Tool Invocations - Chi phí Cực Đắt: Tốn USD thực tế và 1-20 giây tính toán):
+     Chỉ được kích hoạt KHI VÀ CHỈ KHI vượt qua toàn bộ 4 Cổng kiểm duyệt trên.
+2. Chứng minh Ngắn mạch (Short-Circuit Proof) Không Gọi Các Bước Xử lý Phía sau:
+   - Kiến trúc Middleware Interceptor ngắn mạch: Bất kỳ Cổng nào phát hiện vi phạm sẽ lập tức trả về HTTP response và ngắt chuỗi thực thi (return early), không bao giờ gọi hàm `next()`.
+   - Bộ kiểm thử chứng minh với các Dấu vết Quan sát Được (Observable Traces &amp; Metrics):
+     + Test Gate 1 (Malformed JSON): Gửi body sai cú pháp -&gt; Nhận HTTP 400. Dấu vết: Metric `auth_evaluations_total` không tăng (+0), `model_calls_total` = 0.
+     + Test Gate 2 (Missing Auth): Gửi body chuẩn nhưng không có token -&gt; Nhận HTTP 401. Dấu vết: Metric `redis_quota_lookups_total` không tăng (+0), `model_calls_total` = 0.
+     + Test Gate 3 (Rate Limited): Gửi auth hợp lệ nhưng spam 50 req/s -&gt; Nhận HTTP 429. Dấu vết: Metric `cost_estimator_calls_total` không tăng (+0), `model_calls_total` = 0.
+     + Test Gate 4 (Budget Exceeded): Gửi request prompt 100k tokens vượt ngân sách -&gt; Nhận HTTP 402/403. Dấu vết: Metric `provider_invocations_total` không tăng (+0) và số dư tài khoản không bị trừ thêm.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Chiến lược phòng thủ 'Fail-Fast Pipeline' sắp xếp các chốt chặn kiểm duyệt theo thứ tự chi phí tài nguyên tăng dần (từ kiểm tra CPU cục bộ rẻ nhất đến gọi API tính tiền đắt nhất). Việc ngắn mạch tức thì khi phát hiện vi phạm bảo vệ hệ thống khỏi các cuộc tấn công gây cạn kiệt tài chính (Financial Denial of Service - FDoS) và bảo tồn tối đa ngân sách vận hành.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Enterprise Integration Patterns - Fail-Fast Router &amp; AWS Well-Architected Framework - Cost Optimization Pillar</t>
         </is>
       </c>
     </row>
@@ -840,10 +881,25 @@
       <c r="K8" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách ba việc: ai cấp token, token dành cho API nào và token còn hạn/quyền gì.
-Phân tích theo nguyên lý thiết kế: Tách ba việc: ai cấp token, token dành cho API nào và token còn hạn/quyền gì.</t>
+- [1.0 điểm] Lựa chọn chính xác mẫu xác thực OAuth 2.0 Token Exchange / On-Behalf-Of (RFC 8693) cho kịch bản B2B ủy quyền.
+- [1.5 điểm] Phân tích chi tiết các claim an ninh cốt tử: `iss`, `aud` (bắt buộc khớp Audience A), `exp` (short-lived) và `nbf`.
+- [1.5 điểm] Thiết lập cặp định danh kép `sub` (end-user identity) kết hợp `azp/client_id` (B2B partner) cùng phạm vi quyền `scope`.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Lựa chọn Mẫu Xác thực Phù hợp: OAuth 2.0 Token Exchange (RFC 8693) / On-Behalf-Of Flow:
+   - Bối cảnh: Đối tác B2B gọi API thay mặt cho người dùng cuối. Đối tác không được dùng Master API Key tĩnh của mình để truy cập dữ liệu người dùng.
+   - Mô hình áp dụng: Đối tác B2B mang token ủy quyền của người dùng tới Identity Provider (IdP) để thực hiện Token Exchange, nhận về một Delegated Access Token (JWT) có thời hạn ngắn, phân quyền cụ thể và khán giả đích danh.
+2. Các Claim Bắt buộc Cần Kiểm tra Nghiêm ngặt (Claims Verification Matrix):
+   - Claim `iss` (Issuer): Xác minh token được phát hành đúng bởi Authorization Server tin cậy của hệ sinh thái (ví dụ `https://auth.enterprise.com`).
+   - Claim `aud` (Audience - Khán giả đích): BẮT BUỘC kiểm tra `aud == "https://api.enterprise.com/service-A"`. Nếu token có audience của dịch vụ khác (hoặc của Service B), API A phải lập tức từ chối với HTTP 403 Forbidden để ngăn ngừa token bị đối tác mang sang sử dụng trái phép ở API khác.
+   - Claim `exp` (Expiration Time): Kiểm tra thời hạn hiệu lực của token. Token ủy quyền B2B phải là Short-lived Token (thời gian sống từ 15 đến 30 phút). Nếu `current_time &gt;= exp`, từ chối ngay với HTTP 401 Unauthorized.
+   - Claim `nbf` (Not Before): Xác nhận token không được sử dụng trước thời điểm chỉ định trong quá khứ.
+   - Claim `sub` (Subject - Người dùng Ủy quyền): Định danh duy nhất của người dùng cuối (`user_id`) mà đối tác đang đại diện thực thi.
+   - Claim `azp` hoặc `client_id` (Authorized Party - Đối tác B2B): Định danh của đối tác bên thứ ba được ủy quyền gọi thay.
+   - Claim `scope` / `permissions`: Xác định phạm vi các quyền năng cụ thể mà người dùng cho phép đối tác thực hiện trên API A (ví dụ: `documents:read`, không có quyền `documents:delete`).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong kiến trúc tích hợp B2B hiện đại, việc sử dụng mã token đại diện có ràng buộc phạm vi và khán giả đích (Audience-Restricted Delegated Tokens) là tiêu chuẩn bảo mật cốt lõi. Kiểm tra nghiêm ngặt claim `aud` ngăn chặn triệt để tấn công Chuyển tiếp Token (Token Replay/Forwarding Attack), bảo đảm một token phát hành cho dịch vụ A không bao giờ có thể bị lạm dụng để gọi dịch vụ B.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+RFC 8693 (OAuth 2.0 Token Exchange) &amp; RFC 7519 (JSON Web Token - JWT Specification)</t>
         </is>
       </c>
     </row>
@@ -922,10 +978,30 @@
       <c r="K10" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Kiểm riêng ba đường đi: key đúng, key sai và không có key; quan sát status cùng provider_calls.
-Phân tích theo nguyên lý thiết kế: Kiểm riêng ba đường đi: key đúng, key sai và không có key; quan sát status cùng provider_calls.</t>
+- [1.0 điểm] Thiết kế bộ thẩm định API Key với cơ chế băm SHA-256 an toàn và ánh xạ chính xác sang Tenant Identity.
+- [1.5 điểm] Xây dựng bộ test đầy đủ 4 nhánh kiểm thử: Key đúng Tenant 1, Key đúng Tenant 2, Key sai và Thiếu key.
+- [1.5 điểm] Chứng minh nghiêm ngặt bất biến bảo vệ chi phí: các yêu cầu bị từ chối (401) làm tăng provider_calls chính xác bằng 0.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế Bộ Thẩm định Khóa (Client Key Verifier &amp; Tenant Mapping):
+   - Cơ chế Lưu trữ Bảo mật: Tuyệt đối không lưu API Key dạng plain-text. Lưu trữ bảng băm: `API_KEY_HASH (SHA-256) -&gt; TenantContext { tenant_id, name, status, quota }`.
+   - Quy trình Thẩm định tại Gateway Middleware:
+     + Bước 1: Trích xuất `X-API-Key` từ request header. Nếu thiếu header -&gt; Trả về `HTTP 401 Unauthorized` ngay lập tức.
+     + Bước 2: Băm key bằng SHA-256 và tra cứu trong cache bộ nhớ. Nếu không tìm thấy hoặc tenant có status != `ACTIVE` -&gt; Trả về `HTTP 401 Unauthorized` ngay lập tức.
+     + Bước 3: Nếu key hợp lệ, gắn `TenantContext` (chứa `tenant_id`) vào ngữ cảnh của request (`request.state.tenant`) và chuyển tiếp sang Controller/Worker.
+   - Bất biến Cốt tử (Core Invariant): Verifier chạy tại lớp Filter/Middleware trước khi bất kỳ tiến trình nào gọi tới Model Provider; yêu cầu bị từ chối không bao giờ chạm tới hạ tầng downstream.
+2. Thiết kế Bộ Kiểm thử (Verifier Test Suite):
+   - Test Case 1 (Tenant 1 Valid Key):
+     Gửi request với Key của Tenant 1. Khẳng định kết quả HTTP 200 OK. Metric `provider_calls_total{tenant="tenant_1"}` tăng đúng 1 đơn vị.
+   - Test Case 2 (Tenant 2 Valid Key):
+     Gửi request với Key của Tenant 2. Khẳng định kết quả HTTP 200 OK. Metric `provider_calls_total{tenant="tenant_2"}` tăng đúng 1 đơn vị, hoàn toàn độc lập với Tenant 1.
+   - Test Case 3 (Invalid / Forged Key - Negative Test):
+     Gửi request với Key sai `key_invalid_999`. Khẳng định kết quả `HTTP 401 Unauthorized`. Khẳng định cốt tử: Tổng số cuộc gọi `provider_calls_total` của cả hai tenant tăng đúng 0 (+0).
+   - Test Case 4 (Missing Key Header - Negative Test):
+     Gửi request không kèm header xác thực. Khẳng định kết quả `HTTP 401 Unauthorized`. Khẳng định cốt tử: Tổng số cuộc gọi `provider_calls_total` tăng đúng 0 (+0).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Thiết kế xác thực đa người thuê (Multi-Tenant Authentication) yêu cầu sự phân lập tuyệt đối ngay từ cổng vào của hệ thống. Bằng cách thực thi thẩm định khóa trước khi khởi tạo bất kỳ tác vụ nào, hệ thống bảo vệ ngân sách nhà cung cấp dịch vụ khỏi các yêu cầu không hợp lệ, đồng thời gán chính xác chi phí sử dụng cho từng thực thể doanh nghiệp độc lập.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Multi-Tenant Architecture Security Patterns &amp; OWASP API Security - Broken Authentication</t>
         </is>
       </c>
     </row>
@@ -1058,10 +1134,35 @@
       <c r="K13" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách policy thành ba phần: khóa đếm, tham số thuật toán và thông tin trả về khi bị giới hạn.
-Phân tích theo nguyên lý thiết kế: Tách policy thành ba phần: khóa đếm, tham số thuật toán và thông tin trả về khi bị giới hạn.</t>
+- [1.0 điểm] Thiết kế cấu trúc khóa phân tầng kết hợp đầy đủ tier, tenant_id, route và cửa sổ thời gian.
+- [1.5 điểm] Lựa chọn thuật toán Token Bucket / Sliding Window và cấu hình tham số dung lượng/nạp rõ ràng cho từng gói Free/Pro.
+- [1.5 điểm] Quy ước phản hồi 429 chuẩn hóa quốc tế với đầy đủ các headers: Retry-After, RateLimit-Limit, RateLimit-Remaining, RateLimit-Reset.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế Khóa Đếm Giới hạn Tốc độ Phân tầng (Rate Limit Key Schema):
+   - Cấu trúc khóa kết hợp gói dịch vụ, định danh tenant, route định tuyến và cửa sổ thời gian:
+     `rl:{tier}:{tenant_id}:{route_signature}:{window_epoch}`
+     Ví dụ:
+     + Route nặng cho gói Free: `rl:free:t_101:POST_/chat/completions:1698080000`
+     + Route nhẹ cho gói Pro: `rl:pro:t_202:GET_/models:1698080000`
+   - Lợi ích: Tách biệt hoàn toàn quota giữa các gói (Free vs Pro) và giữa các route, ngăn chặn việc gọi dồn dập route nhẹ làm cạn kiệt tài nguyên của route nghiệp vụ chính.
+2. Lựa chọn và Cấu hình Thuật toán Giới hạn Tốc độ:
+   - Thuật toán Áp dụng: Cửa sổ Trượt Kết hợp Token Bucket (Sliding Window Counter / Token Bucket) triển khai trên Redis.
+   - Cấu hình theo Gói (Tier Policy Parameters):
+     + Gói Free: Hạn mức khắt khe, ví dụ route `/chat` cho phép tối đa 10 requests / 60 giây (Burst = 2, Refill = 1 token mỗi 6 giây).
+     + Gói Pro: Hạn mức mở rộng, ví dụ route `/chat` cho phép 120 requests / 60 giây (Burst = 20, Refill = 2 tokens mỗi giây).
+3. Quy ước Phản hồi HTTP 429 và Headers Chuẩn Giúp Client Retry Đúng Lúc:
+   - Khi vượt quá hạn mức, Gateway trả về mã trạng thái chuẩn: `HTTP/1.1 429 Too Many Requests`.
+   - Bắt buộc trả về các Headers chuẩn hóa theo khuyến nghị IETF và RFC 6585:
+     + `Retry-After: 6` (Số giây chính xác client phải chờ trước khi thử lại).
+     + `RateLimit-Limit: 10` (Tổng hạn mức cho phép trong cửa sổ hiện tại).
+     + `RateLimit-Remaining: 0` (Số lượng yêu cầu còn lại trong cửa sổ).
+     + `RateLimit-Reset: 1698080060` (Thời điểm Unix timestamp khi hạn ngạch được làm mới hoàn toàn).
+   - Thân phản hồi JSON chi tiết:
+     `{"error": {"code": "rate_limit_exceeded", "tier": "free", "retry_after_seconds": 6, "message": "Bạn đã đạt hạn ngạch gói Free (10 req/phút). Vui lòng thử lại sau 6 giây hoặc nâng cấp gói Pro."}}`
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Chiến lược kiểm soát lưu lượng phân tầng (Tiered Rate Limiting) giúp bảo vệ hạ tầng khỏi tình trạng quá tải và tối ưu hóa mô hình kinh doanh SaaS. Việc tuân thủ nghiêm ngặt các tiêu chuẩn phản hồi HTTP 429 kèm tiêu đề `Retry-After` giúp các ứng dụng máy khách tự động thiết lập thời gian chờ chính xác, loại bỏ các đợt bắn lại yêu cầu mù quáng (blind retries).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+RFC 6585 (Additional HTTP Status Codes - 429) &amp; IETF Draft: RateLimit Header Fields for HTTP</t>
         </is>
       </c>
     </row>
@@ -1140,10 +1241,46 @@
       <c r="K15" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tìm hai rủi ro riêng: ghi đè do member trùng và race condition giữa các bước đếm–thêm.
-Phân tích theo nguyên lý thiết kế: Tìm hai rủi ro riêng: ghi đè do member trùng và race condition giữa các bước đếm–thêm.</t>
+- [1.0 điểm] Phân tích chính xác lỗi ghi đè member trong Redis ZSET và khắc phục bằng member duy nhất `timestamp:uuid`.
+- [1.5 điểm] Đóng gói thao tác nguyên tử bằng Redis Lua Script kết hợp ZREMRANGEBYSCORE, ZCARD và ZADD loại bỏ race condition.
+- [1.5 điểm] Xây dựng bộ kiểm thử Boundary và Concurrency Isolation chứng minh đếm chính xác khi 2 request đến cùng timestamp.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân tích Nguyên nhân Lỗi và Sửa Cấu trúc Member trong Redis Sorted Set:
+   - Nguyên nhân: Trong Redis Sorted Set (`ZSET`), mỗi phần tử (member) phải là một giá trị duy nhất (unique). Nếu member chỉ là chuỗi timestamp (ví dụ `"1698080000"`), khi hai yêu cầu đồng thời đến trong cùng một mili-giây, yêu cầu thứ hai sẽ cập nhật lại score của member đó thay vì tạo một entry mới. Kết quả là hệ thống đếm thiếu yêu cầu (chỉ đếm 1 thay vì 2), gây rò rỉ hạn ngạch.
+   - Khắc phục Cấu trúc Member: Bắt buộc kết hợp timestamp với một định danh ngẫu nhiên duy nhất (UUIDv4 hoặc Monotonic NanoID):
+     `member = f"{timestamp_epoch}:{uuid4()}"`
+     Score vẫn là timestamp dạng số thực (microsecond float) để phục vụ cho việc lọc theo phạm vi thời gian.
+2. Sửa Thao tác thành Khối Thực thi Nguyên tử (Atomic Lua Script):
+   - Để loại bỏ hoàn toàn hiện tượng tranh chấp điều kiện (Race Condition) giữa bước đếm số lượng và bước ghi nhận, đóng gói toàn bộ logic vào Redis Lua Script:
+     ```lua
+     local key = KEYS[1]
+     local now = tonumber(ARGV[1])
+     local window = tonumber(ARGV[2]) -- 60 seconds
+     local limit = tonumber(ARGV[3])  -- 3 requests
+     local member = ARGV[4]           -- now:uuid
+     local clearBefore = now - window
+     -- 1. Xóa các request cũ ngoài cửa sổ 60s
+     redis.call('ZREMRANGEBYSCORE', key, '-inf', clearBefore)
+     -- 2. Đếm số lượng request hiện tại
+     local currentCount = redis.call('ZCARD', key)
+     -- 3. Kiểm tra và thêm nguyên tử nếu chưa vượt hạn mức
+     if currentCount &lt; limit then
+         redis.call('ZADD', key, now, member)
+         redis.call('EXPIRE', key, window)
+         return {1, limit - currentCount - 1} -- Allowed (1: Chấp nhận, số dư)
+     else
+         return {0, 0} -- Denied (0: Bị từ chối 429)
+     end
+     ```
+3. Thiết kế Kiểm tra Boundary và Isolation:
+   - Boundary Test: Gửi lần lượt 3 yêu cầu hợp lệ trong 60s -&gt; Cả 3 nhận HTTP 200 OK. Gửi yêu cầu thứ 4 tại giây thứ 59 -&gt; Nhận HTTP 429. Chờ đến giây thứ 61, gửi yêu cầu thứ 5 -&gt; Nhận HTTP 200 OK do các yêu cầu cũ đã bị dọn sạch.
+   - Concurrency Isolation Test: Bắn đồng thời 2 yêu cầu Req-1 và Req-2 tại cùng một microsecond khi hệ thống đang ở mức 2/3 requests:
+     + Do member là `now:uuid_1` và `now:uuid_2`, cả hai entry được phân biệt rõ ràng.
+     + Do Lua script chạy đơn luồng nguyên tử trên Redis server, một request được ghi nhận thành công (chạm mốc 3/3), request còn lại lập tức bị từ chối 429. Không có bất kỳ entry nào bị ghi đè.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Triển khai thuật toán Sliding Window Log trên Redis yêu cầu hiểu sâu về đặc tính duy nhất của phần tử trong Sorted Set. Việc tạo member kết hợp timestamp và UUID cùng với việc thực thi nguyên tử qua Lua Script loại trừ hoàn toàn nguy cơ đếm thiếu và race condition trong các kịch bản lưu lượng đồng thời cao.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Redis Documentation - Sorted Sets &amp; Lua Scripting: https://redis.io/commands/zadd/ và Figma Engineering Blog - An Alternative Approach to Rate Limiting</t>
         </is>
       </c>
     </row>
@@ -1210,10 +1347,32 @@
       <c r="K17" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: So sánh chi phí tối đa ước tính với trần trước khi nghĩ đến chi phí thực tế.
-Phân tích theo nguyên lý thiết kế: So sánh chi phí tối đa ước tính với trần trước khi nghĩ đến chi phí thực tế.</t>
+- [1.0 điểm] Đưa ra quyết định chuẩn xác: Từ chối yêu cầu ngay tại cổng tiền kiểm và không gọi model provider.
+- [1.5 điểm] Phân tích căn cứ định lượng rõ ràng: so sánh chi phí ước tính từ tokenizer (0,006 USD) với trần ngân sách (0,004 USD).
+- [1.5 điểm] Thiết lập bằng chứng kiểm toán minh bạch (Audit Trail) ghi nhận vi phạm hạn mức chi phí kèm metric provider_invoked = false.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Quyết định Tiếp nhận / Từ chối (Admission Governance Decision):
+   - Quyết định dứt khoát: TỪ CHỐI YÊU CẦU NGAY TẬP TỨC TẠI CỔNG TIỀN KIỂM (SHORT-CIRCUIT REJECTION).
+   - Mã phản hồi: Trả về `HTTP 400 Bad Request` hoặc `HTTP 403 Forbidden` (hoặc `HTTP 402 Payment Required` đối với tài khoản trả trước).
+   - Tuyệt đối KHÔNG thực hiện cuộc gọi ngược dòng (Downstream Call) tới Model Provider API.
+2. Căn cứ Giới hạn và Bằng chứng Định lượng (Evidence &amp; Quantitative Limits Basis):
+   - Căn cứ Chính sách Trần Chi phí Yêu cầu (Pre-Execution Request Cost Ceiling Policy):
+     + Quy tắc bất biến: `Estimated_Cost &lt;= Request_Cost_Ceiling`.
+     + Số liệu thực tế: `Estimated_Cost = 0.006 USD` &gt; `Request_Cost_Ceiling = 0.004 USD`.
+     + Chi phí ước tính đã vượt quá trần cho phép 150% ngay trước khi thực thi.
+   - Bằng chứng Tính toán từ Bộ phân tích Tokenizer Cục bộ (Local Tokenizer Evidence):
+     + Số lượng token đầu vào (Prompt Tokens): Được đếm chính xác bằng thư viện tokenizer cục bộ (ví dụ: `tiktoken` cho OpenAI hoặc `tokenizers` cho HuggingFace) là $N_{prompt}$ tokens.
+     + Giới hạn token đầu ra tối đa (Configured Max Tokens): Được trích xuất từ tham số `max_tokens` của payload yêu cầu là $N_{max\_output}$ tokens.
+     + Công thức ước tính bảo toàn chi phí xấu nhất (Worst-Case Cost Bound):
+       `Estimated_Cost = (N_prompt * Price_Input_Per_Token) + (N_max_output * Price_Output_Per_Token) = 0.006 USD`.
+3. Dấu vết Kiểm toán và Bảo vệ Tài chính (Audit Evidence Trail):
+   - Ghi nhật ký kiểm toán giao dịch (Structured Audit Log):
+     `{"event": "REQUEST_COST_CEILING_BREACH", "tenant_id": "tenant_xyz", "prompt_tokens": 3200, "max_output_tokens": 1000, "estimated_cost_usd": 0.006, "ceiling_usd": 0.004, "provider_invoked": false, "action": "DENIED"}`.
+   - Lợi ích: Ngăn chặn triệt để rủi ro thâm hụt ngân sách và các cuộc tấn công gây cạn kiệt tài chính (Financial Denial of Service - FDoS) mà không tốn bất kỳ chi phí thực tế nào.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc tiền kiểm soát ngân sách (Pre-Flight Cost Guardrail) là tuyến phòng thủ tài chính quan trọng nhất trong các ứng dụng AI tạo sinh. Bằng cách sử dụng tokenizer cục bộ để tính toán chi phí trần kịch bản xấu nhất trước khi gọi mạng, hệ thống có thể từ chối ngay lập tức các yêu cầu vượt hạn mức, bảo vệ doanh nghiệp khỏi việc tiêu tốn ngân sách ngoài tầm kiểm soát.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+FinOps Foundation - Cost Allocation and Guardrails: https://www.finops.org/framework/ và OpenAI API Pricing &amp; Usage Governance Best Practices</t>
         </is>
       </c>
     </row>
@@ -1292,10 +1451,31 @@
       <c r="K19" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách ba thời điểm: reserve khi admission, đối soát khi có chi phí thực tế và tạo bucket khi sang kỳ mới.
-Phân tích theo nguyên lý thiết kế: Tách ba thời điểm: reserve khi admission, đối soát khi có chi phí thực tế và tạo bucket khi sang kỳ mới.</t>
+- [1.0 điểm] Thiết kế quy trình ghi sổ 2 giai đoạn chuẩn xác: Reserve 1.0 USD khi admission và Reconcile hoàn dư 0.3 USD theo thực tế 0.7 USD.
+- [1.5 điểm] Thiết lập cấu trúc sổ chi tiêu phân lập nghiêm ngặt theo từng tenant_id và billing_period.
+- [1.5 điểm] Xây dựng cơ chế chuyển kỳ tự động: tạo bucket mới theo tháng, đóng băng kỳ cũ và xử lý nhất quán các giao dịch vắt ngang kỳ.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế Ghi sổ Hai Giai đoạn (Two-Phase Ledger Accounting: Reserve &amp; Reconcile):
+   - Giai đoạn 1 (Phong tỏa Tạm tính khi Tiếp nhận - Admission Reservation):
+     + Khi Tenant A gửi yêu cầu, hệ thống tính chi phí ước tính là 1.0 USD.
+     + Thực hiện phong tỏa tạm tính (Hold / Reserve): Trừ 1.0 USD từ số dư khả dụng của Tenant A và ghi vào sổ cái một bản ghi giao dịch trạng thái `PENDING_RESERVED` với mã `hold_id_123`.
+     + Cơ chế này ngăn chặn việc Tenant A gửi đồng thời nhiều yêu cầu vượt quá số dư thực tế.
+   - Giai đoạn 2 (Đối soát Thực tế và Hoàn tiền Thừa - Post-Execution Reconciliation):
+     + Sau khi model hoàn tất sinh dữ liệu, hệ thống đọc usage thực tế từ response (số token vào + ra thực tế) và tính ra chi phí thực tế là 0.7 USD.
+     + Thực hiện quyết toán nguyên tử (Atomic Settlement): Chuyển trạng thái giao dịch sang `SETTLED` với chi phí ghi nhận chính thức là 0.7 USD, đồng thời hoàn trả 0.3 USD (`1.0 USD - 0.7 USD`) vào số dư khả dụng của Tenant A.
+2. Phân lập Sổ Chi tiêu Đa Người thuê (Multi-Tenant Ledger Isolation):
+   - Mỗi tenant sở hữu một sổ chi tiêu riêng biệt, được phân vùng theo cấu trúc khóa độc lập trong cơ sở dữ liệu/Redis:
+     `ledger:{tenant_id}:{billing_period_id}`
+     Ví dụ: Sổ Tenant A: `ledger:tenant_A:2026-10`, Sổ Tenant B: `ledger:tenant_B:2026-10`.
+   - Mọi thao tác ghi sổ, phong tỏa hay đối soát của Tenant A hoàn toàn độc lập và không bao giờ gây khóa hay ảnh hưởng tới số dư của Tenant B.
+3. Thiết kế Cơ chế Chuyển kỳ Kế toán (Billing Period Rollover):
+   - Khởi tạo Khóa Kỳ Mới Tự động: Đúng vào 00:00:00 UTC ngày đầu tháng mới (ví dụ sang tháng 11/2026), hệ thống tự động khởi tạo khóa kỳ mới `ledger:{tenant_id}:2026-11` kèm hạn mức cấp phát mới.
+   - Đóng băng Kỳ cũ (Period Snapshot &amp; Freeze): Kỳ cũ `2026-10` được chuyển sang trạng thái `CLOSED / READ_ONLY` để phục vụ công tác xuất hóa đơn và báo cáo tài chính.
+   - Xử lý Yêu cầu Vắt ngang Kỳ (In-flight Requests across Midnight): Yêu cầu được nhận vào kỳ cũ (với reservation tạo trong kỳ `2026-10`) nhưng hoàn tất ở những giây đầu của kỳ mới vẫn được đối soát và ghi nhận chính xác vào kỳ mà reservation đó đã được sinh ra (`2026-10`), bảo đảm tính toàn vẹn và không làm lệch sổ cái giữa hai tháng.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Quy trình kế toán tài chính phân tán (Distributed FinOps Ledger) trong các nền tảng SaaS AI đòi hỏi sự nhất quán nghiêm ngặt. Việc áp dụng mô hình hai giai đoạn (Phong tỏa tạm tính - Quyết toán đối soát) giải quyết triệt để sự chênh lệch giữa chi phí ước tính và chi phí thực tế, đồng thời cơ chế phân vùng theo kỳ kế toán bảo đảm việc chuyển tháng diễn ra mượt mà và chính xác tuyệt đối.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+FinOps Framework - Allocation and Invoicing Standards: https://www.finops.org/framework/ và Stripe Billing Architecture - Authorize and Settle Patterns</t>
         </is>
       </c>
     </row>
@@ -1374,10 +1554,31 @@
       <c r="K21" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách containment/revoke khỏi cleanup: dọn git history không tự vô hiệu key đã lộ.
-Phân tích theo nguyên lý thiết kế: Tách containment/revoke khỏi cleanup: dọn git history không tự vô hiệu key đã lộ.</t>
+- [1.0 điểm] Phân định rạch ròi quy trình ứng phó theo thứ tự: Ngăn chặn khẩn cấp -&gt; Tạo khóa mới K2 -&gt; Thu hồi khóa cũ K1 -&gt; Dọn dẹp git history.
+- [1.5 điểm] Xử lý an toàn quá trình luân chuyển khóa cho nhiều production consumer mà không gây gián đoạn dịch vụ (Zero-Downtime Rotation).
+- [1.5 điểm] Nêu rõ các bước xác minh độc lập: kiểm tra K1 trả về 401, consumer chạy ổn định với K2, và quét sạch repo với Gitleaks/TruffleHog.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Sắp xếp Quy trình Ứng phó Sự cố Lộ API Key (Incident Response Sequence):
+   - Bước 1 (Emergency Containment - Ngăn chặn Khẩn cấp):
+     + Truy cập ngay bảng điều khiển của nhà cung cấp model (Provider Dashboard).
+     + Thu hẹp quyền hạn của API Key bị lộ (K1): Gán ngay IP Whitelist hoặc hạn chế CORS nếu hỗ trợ, hoặc đặt Rate Limit khắt khe để giảm thiểu thiệt hại khai thác.
+   - Bước 2 (Credential Generation &amp; Dual-Key Deployment - Tạo và Triển khai Khóa Mới):
+     + Tạo API Key mới (K2) tuân thủ nguyên tắc quyền tối thiểu (Least Privilege), chỉ cấp các quyền cần thiết cho ứng dụng.
+     + Cập nhật K2 vào hệ thống quản lý bí mật trung tâm (Cloud Secret Manager / Vault).
+     + Kích hoạt quy trình cập nhật cấu hình cho các consumer production mà không cần dừng dịch vụ (Zero-Downtime Secret Rotation). Duy trì song song K1 và K2 trong một cửa sổ ngắn (12-24 giờ).
+   - Bước 3 (Hard Revocation of Compromised Key - Thu hồi Triệt để Khóa Lộ):
+     + Theo dõi telemetry: Khi số lượng request sử dụng K1 giảm về 0, thực hiện thu hồi vĩnh viễn (Revoke / Delete) K1 trên console nhà cung cấp. Bất kỳ ai cố gắng dùng K1 đều sẽ bị từ chối với HTTP 401.
+   - Bước 4 (Repository Sanitization &amp; Log Cleanup - Làm sạch Lịch sử Mã nguồn):
+     + Sử dụng công cụ chuyên dụng như `git-filter-repo` hoặc BFG Repo-Cleaner để loại bỏ hoàn toàn chuỗi bí mật khỏi toàn bộ commit history của git, sau đó force-push lên repository trung tâm.
+     + Xóa các log build CI/CD đã lưu trữ có chứa chuỗi bí mật.
+2. Các Bước Xác minh Thực tế (Verification Steps):
+   - Xác minh 1 (Key Revocation Verification): Gửi HTTP request trực tiếp tới Model Provider bằng API key cũ K1 -&gt; Xác nhận nhận mã lỗi `HTTP 401 Unauthorized`.
+   - Xác minh 2 (Production Traffic Continuity): Kiểm tra dashboard ứng dụng và log hệ thống, xác nhận 100% các consumer production đang giao tiếp thành công với K2 (HTTP 200).
+   - Xác minh 3 (Secret Scanning Verification): Chạy công cụ quét bí mật tự động (Gitleaks / TruffleHog) trên toàn bộ git repo và CI pipelines -&gt; Khẳng định kết quả 0 findings.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Khi sự cố rò rỉ thông tin xác thực xảy ra trong môi trường sản xuất có nhiều người dùng phụ thuộc, việc vội vàng thu hồi khóa ngay lập tức có thể gây ra sự cố gián đoạn dịch vụ diện rộng (Self-Inflicted Outage). Quy trình luân chuyển khóa hai giai đoạn (Dual-Key Rotation) kết hợp ngăn chặn khẩn cấp và làm sạch lịch sử git bảo đảm an ninh tối đa mà vẫn duy trì tính liên tục của hoạt động kinh doanh.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+NIST SP 800-61 Rev. 2 (Computer Security Incident Handling Guide) &amp; OWASP Secrets Management Cheat Sheet</t>
         </is>
       </c>
     </row>
